--- a/test_data/RegBriefings/RegBriefings World Tax Brief/RegBriefings World Tax Brief_Test_Cases.xlsx
+++ b/test_data/RegBriefings/RegBriefings World Tax Brief/RegBriefings World Tax Brief_Test_Cases.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>World Tax Brief correctly shows 13 real country entries (16 with 'Full Story' links on this environment).</t>
+          <t>World Tax Brief correctly shows 15 real country entries (16 with 'Full Story' links on this environment).</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Search correctly filtered from 13 to 1 entries, keeping 'Australia' visible.</t>
+          <t>Search correctly filtered from 15 to 1 entries, keeping 'Algeria' visible.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Searching 'Australia' leaves only matching entries, still visible</t>
+          <t>[PASS] Searching 'Algeria' leaves only matching entries, still visible</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Clearing the search box correctly restored all 13 entries.</t>
+          <t>Clearing the search box correctly restored all 15 entries.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
